--- a/notes/costs/vision_models_2026-09-28.xlsx
+++ b/notes/costs/vision_models_2026-09-28.xlsx
@@ -891,7 +891,6 @@
           <t>Qwen: Qwen3.8 27B (free)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -940,7 +939,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -953,7 +951,6 @@
           <t>Dots Studio: Dots3-Note Preview (free)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1002,7 +999,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1015,7 +1011,6 @@
           <t>Thinking Machines: Inkling Small (free)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1064,7 +1059,6 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1077,7 +1071,6 @@
           <t>Thinking Machines: Inkling (free)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1126,7 +1119,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1139,7 +1131,6 @@
           <t>NVIDIA: Nemotron 3 Nano Omni (free)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1188,7 +1179,6 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1201,7 +1191,6 @@
           <t>Google: Gemma 4 26B A4B  (free)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1250,7 +1239,6 @@
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1263,7 +1251,6 @@
           <t>Google: Gemma 4 31B (free)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1312,7 +1299,6 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1325,7 +1311,6 @@
           <t>Free Models Router</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1374,7 +1359,6 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1387,7 +1371,6 @@
           <t>DeepSeek: DeepSeek Flash Latest</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1438,7 +1421,6 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1515,7 +1497,6 @@
           <t>inclusionAI: Ling 3.0 Flash VL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1529,7 +1510,6 @@
       <c r="F13" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" s="11" t="n">
         <v>0.021</v>
       </c>
@@ -1562,7 +1542,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1575,7 +1554,6 @@
           <t>Qwen: Qwen3.7 Flash</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1589,7 +1567,6 @@
       <c r="F14" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" s="11" t="n">
         <v>0.03</v>
       </c>
@@ -1624,7 +1601,6 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1637,7 +1613,6 @@
           <t>OpenAI: GPT-5 Nano</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1651,7 +1626,6 @@
       <c r="F15" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" s="11" t="n">
         <v>0.05</v>
       </c>
@@ -1684,7 +1658,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1697,7 +1670,6 @@
           <t>Meta: Muse Spark 1.3 Contributor</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1711,7 +1683,6 @@
       <c r="F16" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -1744,7 +1715,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1757,7 +1727,6 @@
           <t>Meta: Muse Spark 1.2 Contributor</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1771,7 +1740,6 @@
       <c r="F17" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -1804,7 +1772,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1817,7 +1784,6 @@
           <t>Z.ai: GLM Flash Latest</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1868,7 +1834,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1881,7 +1846,6 @@
           <t>Xiaomi: MiMo-V2.6-Flash</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1895,7 +1859,6 @@
       <c r="F19" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" s="11" t="n">
         <v>0.14</v>
       </c>
@@ -1928,7 +1891,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1941,7 +1903,6 @@
           <t>Xiaomi: MiMo-V2.5</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1955,7 +1916,6 @@
       <c r="F20" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" s="11" t="n">
         <v>0.14</v>
       </c>
@@ -1988,7 +1948,6 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2001,7 +1960,6 @@
           <t>Mistral: Ministral 3 3B 2512</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2015,7 +1973,6 @@
       <c r="F21" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -2048,7 +2005,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2061,7 +2017,6 @@
           <t>Google: Gemini 2.5 Flash Lite</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2075,7 +2030,6 @@
       <c r="F22" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -2129,7 +2083,6 @@
           <t>OpenAI: GPT-6 Luna Pro</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2143,7 +2096,6 @@
       <c r="F23" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -2178,7 +2130,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -2257,7 +2208,6 @@
           <t>OpenAI: GPT Luna Latest</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2310,7 +2260,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2323,7 +2272,6 @@
           <t>Mistral: Ministral 3 8B 2512</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2337,7 +2285,6 @@
       <c r="F26" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -2370,7 +2317,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2383,7 +2329,6 @@
           <t>Mistral: Mistral Small 4</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2397,7 +2342,6 @@
       <c r="F27" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -2430,7 +2374,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2443,7 +2386,6 @@
           <t>Qwen: Qwen3.8 Omni Flash</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2457,7 +2399,6 @@
       <c r="F28" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -2490,7 +2431,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2503,7 +2443,6 @@
           <t>Qwen: Qwen3.8 Flash</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2517,7 +2456,6 @@
       <c r="F29" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -2552,7 +2490,6 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2565,7 +2502,6 @@
           <t>OpenAI: GPT-4.1 Nano</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2579,7 +2515,6 @@
       <c r="F30" s="10" t="n">
         <v>1047576</v>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -2612,7 +2547,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2625,7 +2559,6 @@
           <t>Mistral: Ministral 3 14B 2512</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2639,7 +2572,6 @@
       <c r="F31" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -2672,7 +2604,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2749,7 +2680,6 @@
           <t>OpenAI: GPT-5.4 Nano</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2763,7 +2693,6 @@
       <c r="F33" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -2796,7 +2725,6 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2809,7 +2737,6 @@
           <t>Google: Gemma 3 27B</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2823,7 +2750,6 @@
       <c r="F34" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" s="11" t="n">
         <v>0.08</v>
       </c>
@@ -2856,7 +2782,6 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2869,7 +2794,6 @@
           <t>OpenAI: GPT-5.6 Luna Pro</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2883,7 +2807,6 @@
       <c r="F35" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -2918,7 +2841,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2931,7 +2853,6 @@
           <t>OpenAI: GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2945,7 +2866,6 @@
       <c r="F36" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -2980,7 +2900,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2993,7 +2912,6 @@
           <t>Google: Gemma 3 12B</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3007,7 +2925,6 @@
       <c r="F37" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" s="11" t="n">
         <v>0.05</v>
       </c>
@@ -3038,7 +2955,6 @@
           <t>2025-03-13</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3051,7 +2967,6 @@
           <t>Google: Gemini 3.1 Flash Lite</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3065,7 +2980,6 @@
       <c r="F38" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -3102,7 +3016,6 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3115,7 +3028,6 @@
           <t>Google: Gemini 3.1 Flash Lite Preview</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3129,7 +3041,6 @@
       <c r="F39" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -3166,7 +3077,6 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -3243,7 +3153,6 @@
           <t xml:space="preserve">Google: Gemma 4 26B A4B </t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3257,7 +3166,6 @@
       <c r="F41" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" s="11" t="n">
         <v>0.09</v>
       </c>
@@ -3290,7 +3198,6 @@
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3303,7 +3210,6 @@
           <t>Google: Gemma 4 31B</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3317,7 +3223,6 @@
       <c r="F42" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" s="11" t="n">
         <v>0.09</v>
       </c>
@@ -3350,7 +3255,6 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3363,7 +3267,6 @@
           <t>OpenAI: GPT-5 Mini</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3377,7 +3280,6 @@
       <c r="F43" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -3410,7 +3312,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3423,7 +3324,6 @@
           <t>Amazon: Nova Lite 1.0</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3437,7 +3337,6 @@
       <c r="F44" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" s="11" t="n">
         <v>0.06</v>
       </c>
@@ -3468,7 +3367,6 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3481,7 +3379,6 @@
           <t>StepFun: Step 3.7 Flash</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3495,7 +3392,6 @@
       <c r="F45" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -3528,7 +3424,6 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3541,7 +3436,6 @@
           <t>OpenAI: GPT-5.1-Codex-Mini</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3555,7 +3449,6 @@
       <c r="F46" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -3588,7 +3481,6 @@
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3601,7 +3493,6 @@
           <t>Qwen: Qwen3.5-Flash</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3615,7 +3506,6 @@
       <c r="F47" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" s="11" t="n">
         <v>0.065</v>
       </c>
@@ -3646,7 +3536,6 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3659,7 +3548,6 @@
           <t>Qwen: Qwen3.6 35B A3B</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3673,7 +3561,6 @@
       <c r="F48" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -3706,7 +3593,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3719,7 +3605,6 @@
           <t>Google: Gemini 3.5 Flash Lite</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3733,7 +3618,6 @@
       <c r="F49" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -3770,7 +3654,6 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3783,7 +3666,6 @@
           <t>Google: Gemini 2.5 Flash</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3797,7 +3679,6 @@
       <c r="F50" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -3851,7 +3732,6 @@
           <t>DeepSeek: DeepSeek V4 Flash Vision Exp</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3865,7 +3745,6 @@
       <c r="F51" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" s="11" t="n">
         <v>0.44</v>
       </c>
@@ -3898,7 +3777,6 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3911,7 +3789,6 @@
           <t>Meta: Muse Glimmer 30B</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3925,7 +3802,6 @@
       <c r="F52" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -3958,7 +3834,6 @@
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3971,7 +3846,6 @@
           <t>ByteDance Seed: Seed 1.6 Flash</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3985,7 +3859,6 @@
       <c r="F53" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" s="11" t="n">
         <v>0.075</v>
       </c>
@@ -4033,7 +3906,6 @@
           <t>PrismML: Ternary Bonsai 2 27B</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4047,7 +3919,6 @@
       <c r="F54" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" s="11" t="n">
         <v>0.075</v>
       </c>
@@ -4078,7 +3949,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4091,7 +3961,6 @@
           <t>OpenAI: GPT-4o-mini</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4105,7 +3974,6 @@
       <c r="F55" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -4138,7 +4006,6 @@
           <t>2024-07-18</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4151,7 +4018,6 @@
           <t>OpenAI: GPT-4o-mini (2024-07-18)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4165,7 +4031,6 @@
       <c r="F56" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -4198,7 +4063,6 @@
           <t>2024-07-18</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4211,7 +4075,6 @@
           <t>Z.ai: GLM 4.6V</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4225,7 +4088,6 @@
       <c r="F57" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -4258,7 +4120,6 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4271,7 +4132,6 @@
           <t>Mistral: Mistral Medium 3.1</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4285,7 +4145,6 @@
       <c r="F58" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" s="11" t="n">
         <v>0.4</v>
       </c>
@@ -4318,7 +4177,6 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4331,7 +4189,6 @@
           <t>Mistral: Mistral Medium 3</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4345,7 +4202,6 @@
       <c r="F59" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" s="11" t="n">
         <v>0.4</v>
       </c>
@@ -4378,7 +4234,6 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4391,7 +4246,6 @@
           <t>MiniMax: MiniMax M3</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4405,7 +4259,6 @@
       <c r="F60" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -4438,7 +4291,6 @@
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4451,7 +4303,6 @@
           <t>Mistral: Mistral Small 3.2 24B</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4465,7 +4316,6 @@
       <c r="F61" s="10" t="n">
         <v>256000</v>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" s="11" t="n">
         <v>0.09375</v>
       </c>
@@ -4496,7 +4346,6 @@
           <t>2025-06-20</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4509,7 +4358,6 @@
           <t>Reka Edge</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4523,7 +4371,6 @@
       <c r="F62" s="10" t="n">
         <v>16384</v>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -4554,7 +4401,6 @@
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4567,7 +4413,6 @@
           <t>Qwen: Qwen3.5-9B</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4581,7 +4426,6 @@
       <c r="F63" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -4612,7 +4456,6 @@
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4625,7 +4468,6 @@
           <t>Qwen: Qwen3.7 Plus</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4639,7 +4481,6 @@
       <c r="F64" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" s="11" t="n">
         <v>0.32</v>
       </c>
@@ -4674,7 +4515,6 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4687,7 +4527,6 @@
           <t>Meta: Llama 4 Scout</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4701,7 +4540,6 @@
       <c r="F65" s="10" t="n">
         <v>1310720</v>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -4732,7 +4570,6 @@
           <t>2025-04-05</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4745,7 +4582,6 @@
           <t>ByteDance Seed: Seed-2.0-Mini</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4759,7 +4595,6 @@
       <c r="F66" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -4790,7 +4625,6 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4803,7 +4637,6 @@
           <t>Google: Gemini 3 Flash Preview</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4817,7 +4650,6 @@
       <c r="F67" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" s="11" t="n">
         <v>0.5</v>
       </c>
@@ -4854,7 +4686,6 @@
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4867,7 +4698,6 @@
           <t>Qwen: Qwen3 VL 32B Instruct</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4881,7 +4711,6 @@
       <c r="F68" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" s="11" t="n">
         <v>0.104</v>
       </c>
@@ -4929,7 +4758,6 @@
           <t>Mistral: Mistral Large 3 2512</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4943,7 +4771,6 @@
       <c r="F69" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" s="11" t="n">
         <v>0.5</v>
       </c>
@@ -4976,7 +4803,6 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4989,7 +4815,6 @@
           <t>Qwen: Qwen3 VL 8B Instruct</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5003,7 +4828,6 @@
       <c r="F70" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" s="11" t="n">
         <v>0.117</v>
       </c>
@@ -5051,7 +4875,6 @@
           <t>Qwen: Qwen3 VL 235B A22B Instruct</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5065,7 +4888,6 @@
       <c r="F71" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" s="11" t="n">
         <v>0.21</v>
       </c>
@@ -5098,7 +4920,6 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5111,7 +4932,6 @@
           <t>MoonshotAI: Kimi K2.5</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5125,7 +4945,6 @@
       <c r="F72" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" s="11" t="n">
         <v>0.45</v>
       </c>
@@ -5158,7 +4977,6 @@
           <t>2026-01-27</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5171,7 +4989,6 @@
           <t>Z.ai: GLM 5.3 FlashX</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5185,7 +5002,6 @@
       <c r="F73" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" s="11" t="n">
         <v>0.37</v>
       </c>
@@ -5218,7 +5034,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5231,7 +5046,6 @@
           <t>Qwen: Qwen3.8 27B</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5245,7 +5059,6 @@
       <c r="F74" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" s="11" t="n">
         <v>0.42</v>
       </c>
@@ -5278,7 +5091,6 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5291,7 +5103,6 @@
           <t>OpenAI: GPT-4.1 Mini</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5305,7 +5116,6 @@
       <c r="F75" s="10" t="n">
         <v>1047576</v>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" s="11" t="n">
         <v>0.4</v>
       </c>
@@ -5338,7 +5148,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5351,7 +5160,6 @@
           <t>Thinking Machines: Inkling Small</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5365,7 +5173,6 @@
       <c r="F76" s="10" t="n">
         <v>524288</v>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" s="11" t="n">
         <v>0.45</v>
       </c>
@@ -5398,7 +5205,6 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -5479,7 +5285,6 @@
           <t>Google: Gemini 3.7 Flash</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5493,7 +5298,6 @@
       <c r="F78" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" s="11" t="n">
         <v>0.75</v>
       </c>
@@ -5530,7 +5334,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5543,7 +5346,6 @@
           <t>Google: Gemini 3.6 Flash</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5557,7 +5359,6 @@
       <c r="F79" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" s="11" t="n">
         <v>0.75</v>
       </c>
@@ -5594,7 +5395,6 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5607,7 +5407,6 @@
           <t>Google: Gemini Flash Latest</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5662,7 +5461,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5675,7 +5473,6 @@
           <t>Qwen: Qwen3 VL 30B A3B Instruct</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5689,7 +5486,6 @@
       <c r="F81" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -5720,7 +5516,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5733,7 +5528,6 @@
           <t>Perceptron: Perceptron Mk1.5</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5747,7 +5541,6 @@
       <c r="F82" s="10" t="n">
         <v>36864</v>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -5778,7 +5571,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5791,7 +5583,6 @@
           <t>Qwen: Qwen3.5-35B-A3B</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5805,7 +5596,6 @@
       <c r="F83" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" s="11" t="n">
         <v>0.1625</v>
       </c>
@@ -5836,7 +5626,6 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5849,7 +5638,6 @@
           <t>Z.ai: GLM 4.5V</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5863,7 +5651,6 @@
       <c r="F84" s="10" t="n">
         <v>65536</v>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" s="11" t="n">
         <v>0.6</v>
       </c>
@@ -5896,7 +5683,6 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5909,7 +5695,6 @@
           <t>OpenAI: GPT Mini Latest</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5960,7 +5745,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5973,7 +5757,6 @@
           <t>OpenAI: GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5987,7 +5770,6 @@
       <c r="F86" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" s="11" t="n">
         <v>0.75</v>
       </c>
@@ -6020,7 +5802,6 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6033,7 +5814,6 @@
           <t>Cohere: Command A+</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6047,7 +5827,6 @@
       <c r="F87" s="10" t="n">
         <v>192000</v>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -6080,7 +5859,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6093,7 +5871,6 @@
           <t>Meta: Llama 4 Maverick</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6107,7 +5884,6 @@
       <c r="F88" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" s="11" t="n">
         <v>0.1875</v>
       </c>
@@ -6138,7 +5914,6 @@
           <t>2025-04-05</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6151,7 +5926,6 @@
           <t>Qwen: Qwen3 VL 8B Thinking</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6165,7 +5939,6 @@
       <c r="F89" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" s="11" t="n">
         <v>0.18</v>
       </c>
@@ -6213,7 +5986,6 @@
           <t>Qwen: Qwen3.6 Flash</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6227,7 +5999,6 @@
       <c r="F90" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" s="11" t="n">
         <v>0.1875</v>
       </c>
@@ -6260,7 +6031,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6273,7 +6043,6 @@
           <t>Qwen: Qwen3.5-27B</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6287,7 +6056,6 @@
       <c r="F91" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" s="11" t="n">
         <v>0.195</v>
       </c>
@@ -6318,7 +6086,6 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6331,7 +6098,6 @@
           <t>Qwen: Qwen3 VL 30B A3B Thinking</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6345,7 +6111,6 @@
       <c r="F92" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -6393,7 +6158,6 @@
           <t>MoonshotAI: Kimi K2.6</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6407,7 +6171,6 @@
       <c r="F93" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" s="11" t="n">
         <v>0.65</v>
       </c>
@@ -6440,7 +6203,6 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6453,7 +6215,6 @@
           <t>Anthropic: Claude Haiku Latest</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6506,7 +6267,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6519,7 +6279,6 @@
           <t>Anthropic: Claude Haiku 4.5</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6533,7 +6292,6 @@
       <c r="F95" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" s="11" t="n">
         <v>1</v>
       </c>
@@ -6568,7 +6326,6 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6581,7 +6338,6 @@
           <t>MoonshotAI: Kimi K2.7 Code</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6595,7 +6351,6 @@
       <c r="F96" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" s="11" t="n">
         <v>0.6562</v>
       </c>
@@ -6628,7 +6383,6 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6641,7 +6395,6 @@
           <t>Sakana: Sakana Namazu</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6655,7 +6408,6 @@
       <c r="F97" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" s="11" t="n">
         <v>0.95</v>
       </c>
@@ -6688,7 +6440,6 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6701,7 +6452,6 @@
           <t>ByteDance Seed: Seed-2.0-Lite</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6715,7 +6465,6 @@
       <c r="F98" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -6746,7 +6495,6 @@
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6759,7 +6507,6 @@
           <t>ByteDance Seed: Seed 1.6</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6773,7 +6520,6 @@
       <c r="F99" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -6821,7 +6567,6 @@
           <t>Qwen: Qwen3.5 Plus 2026-02-15</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6835,7 +6580,6 @@
       <c r="F100" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" s="11" t="n">
         <v>0.26</v>
       </c>
@@ -6866,7 +6610,6 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6879,7 +6622,6 @@
           <t>Qwen: Qwen3.5-122B-A10B</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6893,7 +6635,6 @@
       <c r="F101" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" s="11" t="n">
         <v>0.26</v>
       </c>
@@ -6924,7 +6665,6 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6937,7 +6677,6 @@
           <t>Google: Gemini 2.5 Pro</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6951,7 +6690,6 @@
       <c r="F102" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7005,7 +6743,6 @@
           <t>Google: Gemini 2.5 Pro Preview 06-05</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7019,7 +6756,6 @@
       <c r="F103" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7056,7 +6792,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7069,7 +6804,6 @@
           <t>Qwen: Qwen3.5 397B A17B</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7083,7 +6817,6 @@
       <c r="F104" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" s="11" t="n">
         <v>0.55</v>
       </c>
@@ -7116,7 +6849,6 @@
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7129,7 +6861,6 @@
           <t>Thinking Machines: Inkling</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7143,7 +6874,6 @@
       <c r="F105" s="10" t="n">
         <v>524288</v>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" s="11" t="n">
         <v>1</v>
       </c>
@@ -7176,7 +6906,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -7253,7 +6982,6 @@
           <t>Meta: Muse Spark 1.2</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7267,7 +6995,6 @@
       <c r="F107" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7300,7 +7027,6 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7313,7 +7039,6 @@
           <t>Meta: Muse Spark 1.1</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7327,7 +7052,6 @@
       <c r="F108" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7360,7 +7084,6 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7373,7 +7096,6 @@
           <t>SpaceXAI: Grok Build 0.1</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7387,7 +7109,6 @@
       <c r="F109" s="10" t="n">
         <v>256000</v>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" s="11" t="n">
         <v>1</v>
       </c>
@@ -7420,7 +7141,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7433,7 +7153,6 @@
           <t>OpenAI: GPT-5.1-Codex-Max</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7447,7 +7166,6 @@
       <c r="F110" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7480,7 +7198,6 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7493,7 +7210,6 @@
           <t>OpenAI: GPT-5.1</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7507,7 +7223,6 @@
       <c r="F111" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7540,7 +7255,6 @@
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7553,7 +7267,6 @@
           <t>OpenAI: GPT-5</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7567,7 +7280,6 @@
       <c r="F112" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7600,7 +7312,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7613,7 +7324,6 @@
           <t>Google: Gemini 3.5 Flash</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7627,7 +7337,6 @@
       <c r="F113" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" s="11" t="n">
         <v>1.5</v>
       </c>
@@ -7664,7 +7373,6 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7677,7 +7385,6 @@
           <t>OpenAI: GPT-5.1-Codex</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7691,7 +7398,6 @@
       <c r="F114" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7724,7 +7430,6 @@
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7737,7 +7442,6 @@
           <t>Qwen: Qwen3.5 Plus 2026-04-20</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7751,7 +7455,6 @@
       <c r="F115" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -7784,7 +7487,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7797,7 +7499,6 @@
           <t>Amazon: Nova 2 Lite</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7811,7 +7512,6 @@
       <c r="F116" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -7842,7 +7542,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7855,7 +7554,6 @@
           <t>SpaceXAI: Grok 4.3</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7869,7 +7567,6 @@
       <c r="F117" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7902,7 +7599,6 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7915,7 +7611,6 @@
           <t>SpaceXAI: Grok 4.20</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7929,7 +7624,6 @@
       <c r="F118" s="10" t="n">
         <v>2000000</v>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -7962,7 +7656,6 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7975,7 +7668,6 @@
           <t>Qwen: Qwen3.6 27B</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7989,7 +7681,6 @@
       <c r="F119" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" s="11" t="n">
         <v>0.32</v>
       </c>
@@ -8020,7 +7711,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8033,7 +7723,6 @@
           <t>Qwen: Qwen3.6 Plus</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8047,7 +7736,6 @@
       <c r="F120" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" s="11" t="n">
         <v>0.325</v>
       </c>
@@ -8080,7 +7768,6 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8093,7 +7780,6 @@
           <t>Mistral: Mistral Small 3.1 24B</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8107,7 +7793,6 @@
       <c r="F121" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" s="11" t="n">
         <v>0.351</v>
       </c>
@@ -8138,7 +7823,6 @@
           <t>2025-03-17</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8151,7 +7835,6 @@
           <t>Z.ai: GLM 5V Turbo</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8165,7 +7848,6 @@
       <c r="F122" s="10" t="n">
         <v>202752</v>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" s="11" t="n">
         <v>1.2</v>
       </c>
@@ -8198,7 +7880,6 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8211,7 +7892,6 @@
           <t>OpenAI: o4 Mini High</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8225,7 +7905,6 @@
       <c r="F123" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" s="11" t="n">
         <v>1.1</v>
       </c>
@@ -8258,7 +7937,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8271,7 +7949,6 @@
           <t>OpenAI: o4 Mini</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8285,7 +7962,6 @@
       <c r="F124" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" s="11" t="n">
         <v>1.1</v>
       </c>
@@ -8318,7 +7994,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8331,7 +8006,6 @@
           <t>Google: Nano Banana Pro (Gemini 3 Pro Image)</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8345,7 +8019,6 @@
       <c r="F125" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" s="11" t="n">
         <v>2</v>
       </c>
@@ -8382,7 +8055,6 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8395,7 +8067,6 @@
           <t>Google: Gemini Pro Latest</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8450,7 +8121,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8463,7 +8133,6 @@
           <t>Google: Gemini 3.1 Pro Preview Custom Tools</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8477,7 +8146,6 @@
       <c r="F127" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" s="11" t="n">
         <v>2</v>
       </c>
@@ -8514,7 +8182,6 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8527,7 +8194,6 @@
           <t>Google: Gemini 3.1 Pro Preview</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8541,7 +8207,6 @@
       <c r="F128" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" s="11" t="n">
         <v>2</v>
       </c>
@@ -8578,7 +8243,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8591,7 +8255,6 @@
           <t>Qwen: Qwen3 VL 235B A22B Thinking</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8605,7 +8268,6 @@
       <c r="F129" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" s="11" t="n">
         <v>0.4</v>
       </c>
@@ -8653,7 +8315,6 @@
           <t>OpenAI: GPT-5.3-Codex</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8667,7 +8328,6 @@
       <c r="F130" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" s="11" t="n">
         <v>1.75</v>
       </c>
@@ -8700,7 +8360,6 @@
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8713,7 +8372,6 @@
           <t>OpenAI: GPT-5.2-Codex</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8727,7 +8385,6 @@
       <c r="F131" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" s="11" t="n">
         <v>1.75</v>
       </c>
@@ -8760,7 +8417,6 @@
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8773,7 +8429,6 @@
           <t>OpenAI: GPT-5.2 Chat</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8787,7 +8442,6 @@
       <c r="F132" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" s="11" t="n">
         <v>1.75</v>
       </c>
@@ -8820,7 +8474,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8833,7 +8486,6 @@
           <t>OpenAI: GPT-5.2</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8847,7 +8499,6 @@
       <c r="F133" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" s="11" t="n">
         <v>1.75</v>
       </c>
@@ -8880,7 +8531,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8893,7 +8543,6 @@
           <t>MoonshotAI: Kimi Latest</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8944,7 +8593,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8957,7 +8605,6 @@
           <t>OpenAI: GPT-6 Sol Pro</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8971,7 +8618,6 @@
       <c r="F135" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" s="11" t="n">
         <v>2</v>
       </c>
@@ -9006,7 +8652,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9019,7 +8664,6 @@
           <t>OpenAI: GPT-6 Sol</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9033,7 +8677,6 @@
       <c r="F136" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" s="11" t="n">
         <v>2</v>
       </c>
@@ -9068,7 +8711,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9081,7 +8723,6 @@
           <t>OpenAI: GPT Sol Latest</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9134,7 +8775,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9147,7 +8787,6 @@
           <t>OpenAI: GPT-5.6 Sol Pro</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9161,7 +8800,6 @@
       <c r="F138" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" s="11" t="n">
         <v>2</v>
       </c>
@@ -9196,7 +8834,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9209,7 +8846,6 @@
           <t>OpenAI: GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9223,7 +8859,6 @@
       <c r="F139" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" s="11" t="n">
         <v>2</v>
       </c>
@@ -9258,7 +8893,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9271,7 +8905,6 @@
           <t>Anthropic: Claude Sonnet 5</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9285,7 +8918,6 @@
       <c r="F140" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" s="11" t="n">
         <v>2</v>
       </c>
@@ -9320,7 +8952,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9333,7 +8964,6 @@
           <t>Anthropic: Claude Sonnet Latest</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9386,7 +9016,6 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9399,7 +9028,6 @@
           <t>Sakana: Fugu Max</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9413,7 +9041,6 @@
       <c r="F142" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" s="11" t="n">
         <v>2</v>
       </c>
@@ -9446,7 +9073,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9459,7 +9085,6 @@
           <t>OpenAI: GPT Terra Latest</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9512,7 +9137,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9525,7 +9149,6 @@
           <t>OpenAI: GPT-5.6 Terra Pro</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9539,7 +9162,6 @@
       <c r="F144" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" s="11" t="n">
         <v>2</v>
       </c>
@@ -9574,7 +9196,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9587,7 +9208,6 @@
           <t>OpenAI: GPT-5.6 Terra</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9601,7 +9221,6 @@
       <c r="F145" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" s="11" t="n">
         <v>2</v>
       </c>
@@ -9636,7 +9255,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9649,7 +9267,6 @@
           <t>Qwen: Qwen3.8 Max (0902)</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9663,7 +9280,6 @@
       <c r="F146" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" s="11" t="n">
         <v>2</v>
       </c>
@@ -9698,7 +9314,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9711,7 +9326,6 @@
           <t>ByteDance Seed: Seed 2.1 Turbo</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9725,7 +9339,6 @@
       <c r="F147" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" s="11" t="n">
         <v>0.5</v>
       </c>
@@ -9756,7 +9369,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9769,7 +9381,6 @@
           <t>ByteDance Seed: Seed-2.0-Code</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9783,7 +9394,6 @@
       <c r="F148" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" s="11" t="n">
         <v>0.5</v>
       </c>
@@ -9831,7 +9441,6 @@
           <t>SpaceXAI: Grok 4.5</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9845,7 +9454,6 @@
       <c r="F149" s="10" t="n">
         <v>500000</v>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" s="11" t="n">
         <v>2</v>
       </c>
@@ -9878,7 +9486,6 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9891,7 +9498,6 @@
           <t>Pareto</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9905,7 +9511,6 @@
       <c r="F150" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -9938,7 +9543,6 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9951,7 +9555,6 @@
           <t>Xiaomi: MiMo-V2.6-Pro-UltraSpeed</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9965,7 +9568,6 @@
       <c r="F151" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" s="11" t="n">
         <v>4.35</v>
       </c>
@@ -9998,7 +9600,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10011,7 +9612,6 @@
           <t>SpaceXAI: Grok 4.7</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10025,7 +9625,6 @@
       <c r="F152" s="10" t="n">
         <v>500000</v>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" s="11" t="n">
         <v>1.6</v>
       </c>
@@ -10058,7 +9657,6 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10071,7 +9669,6 @@
           <t>xAI: Grok Latest</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10122,7 +9719,6 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10135,7 +9731,6 @@
           <t>OpenAI: GPT-5.4</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10149,7 +9744,6 @@
       <c r="F154" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -10182,7 +9776,6 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10195,7 +9788,6 @@
           <t>Fireworks: Ember-1</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10209,7 +9801,6 @@
       <c r="F155" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" s="11" t="n">
         <v>3</v>
       </c>
@@ -10242,7 +9833,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -10319,7 +9909,6 @@
           <t>SpaceXAI: Grok 4.6</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10333,7 +9922,6 @@
       <c r="F157" s="10" t="n">
         <v>500000</v>
       </c>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" s="11" t="n">
         <v>2</v>
       </c>
@@ -10366,7 +9954,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10379,7 +9966,6 @@
           <t>Anthropic: Claude Sonnet 4.6</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10393,7 +9979,6 @@
       <c r="F158" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" s="11" t="n">
         <v>3</v>
       </c>
@@ -10428,7 +10013,6 @@
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10441,7 +10025,6 @@
           <t>Anthropic: Claude Sonnet 4.5</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10455,7 +10038,6 @@
       <c r="F159" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" s="11" t="n">
         <v>3</v>
       </c>
@@ -10490,7 +10072,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10503,7 +10084,6 @@
           <t>Anthropic: Claude Sonnet 4</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10517,7 +10097,6 @@
       <c r="F160" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" s="11" t="n">
         <v>3</v>
       </c>
@@ -10552,7 +10131,6 @@
           <t>2025-05-22</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10565,7 +10143,6 @@
           <t>OpenAI: o3</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10579,7 +10156,6 @@
       <c r="F161" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" s="11" t="n">
         <v>2</v>
       </c>
@@ -10612,7 +10188,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10625,7 +10200,6 @@
           <t>OpenAI: GPT-4.1</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10639,7 +10213,6 @@
       <c r="F162" s="10" t="n">
         <v>1047576</v>
       </c>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" s="11" t="n">
         <v>2</v>
       </c>
@@ -10672,7 +10245,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -10751,7 +10323,6 @@
           <t>Anthropic: Claude Opus Latest</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10804,7 +10375,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10817,7 +10387,6 @@
           <t>Amazon: Nova Pro 1.0</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10831,7 +10400,6 @@
       <c r="F165" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" s="11" t="n">
         <v>0.7999999999999999</v>
       </c>
@@ -10862,7 +10430,6 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10875,7 +10442,6 @@
           <t>Amazon: Nova Premier 1.0</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10889,7 +10455,6 @@
       <c r="F166" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -10922,7 +10487,6 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10935,7 +10499,6 @@
           <t>Qwen: Qwen3.8 Max Prime</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10949,7 +10512,6 @@
       <c r="F167" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" s="11" t="n">
         <v>4</v>
       </c>
@@ -10982,7 +10544,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10995,7 +10556,6 @@
           <t>Sakana: Fugu Ultra v2</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11009,7 +10569,6 @@
       <c r="F168" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" s="11" t="n">
         <v>5</v>
       </c>
@@ -11042,7 +10601,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11055,7 +10613,6 @@
           <t>Sakana: Fugu Ultra</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11069,7 +10626,6 @@
       <c r="F169" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" s="11" t="n">
         <v>5</v>
       </c>
@@ -11102,7 +10658,6 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11115,7 +10670,6 @@
           <t>OpenAI: GPT Chat Latest</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11129,7 +10683,6 @@
       <c r="F170" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" s="11" t="n">
         <v>5</v>
       </c>
@@ -11162,7 +10715,6 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11175,7 +10727,6 @@
           <t>OpenAI: GPT-5.5</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11189,7 +10740,6 @@
       <c r="F171" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" s="11" t="n">
         <v>5</v>
       </c>
@@ -11222,7 +10772,6 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11235,7 +10784,6 @@
           <t>Anthropic: Claude Opus 5</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11249,7 +10797,6 @@
       <c r="F172" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" s="11" t="n">
         <v>5</v>
       </c>
@@ -11284,7 +10831,6 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11297,7 +10843,6 @@
           <t>Anthropic: Claude Opus 4.8</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11311,7 +10856,6 @@
       <c r="F173" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" s="11" t="n">
         <v>5</v>
       </c>
@@ -11346,7 +10890,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11359,7 +10902,6 @@
           <t>Anthropic: Claude Opus 4.7</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11373,7 +10915,6 @@
       <c r="F174" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" s="11" t="n">
         <v>5</v>
       </c>
@@ -11408,7 +10949,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11421,7 +10961,6 @@
           <t>Anthropic: Claude Opus 4.6</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11435,7 +10974,6 @@
       <c r="F175" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" s="11" t="n">
         <v>5</v>
       </c>
@@ -11470,7 +11008,6 @@
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11483,7 +11020,6 @@
           <t>Anthropic: Claude Opus 4.5</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11497,7 +11033,6 @@
       <c r="F176" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" s="11" t="n">
         <v>5</v>
       </c>
@@ -11532,7 +11067,6 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11545,7 +11079,6 @@
           <t>OpenAI: GPT-4o (2024-11-20)</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11559,7 +11092,6 @@
       <c r="F177" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -11592,7 +11124,6 @@
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11605,7 +11136,6 @@
           <t>OpenAI: GPT-4o (2024-08-06)</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11619,7 +11149,6 @@
       <c r="F178" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -11652,7 +11181,6 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11665,7 +11193,6 @@
           <t>OpenAI: GPT-4o</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11679,7 +11206,6 @@
       <c r="F179" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -11712,7 +11238,6 @@
           <t>2024-05-13</t>
         </is>
       </c>
-      <c r="R179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11725,7 +11250,11 @@
           <t>Mistral: Mistral Medium 3.5</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>cache read 10% per Mistral (not on OpenRouter)</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11739,14 +11268,15 @@
       <c r="F180" s="10" t="n">
         <v>262144</v>
       </c>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="I180" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="J180" s="11" t="n"/>
+      <c r="J180" s="11" t="n">
+        <v>0.15</v>
+      </c>
       <c r="K180" s="11" t="n"/>
       <c r="L180" s="11" t="n"/>
       <c r="M180" s="12">
@@ -11770,7 +11300,6 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="R180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -11849,7 +11378,6 @@
           <t>Anthropic: Claude Fable Latest</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11902,7 +11430,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="R182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11915,7 +11442,6 @@
           <t>OpenAI: GPT Astra Latest</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11968,7 +11494,6 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="R183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
@@ -12047,7 +11572,6 @@
           <t>OpenAI: GPT-6 Astra Pro</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12061,7 +11585,6 @@
       <c r="F185" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" s="11" t="n">
         <v>10</v>
       </c>
@@ -12096,7 +11619,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12109,7 +11631,6 @@
           <t>Anthropic: Claude Fable 5</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12123,7 +11644,6 @@
       <c r="F186" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" s="11" t="n">
         <v>10</v>
       </c>
@@ -12158,7 +11678,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="R186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12171,7 +11690,6 @@
           <t>Anthropic: Claude Opus 4.1</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12185,7 +11703,6 @@
       <c r="F187" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" s="11" t="n">
         <v>15</v>
       </c>
@@ -12220,7 +11737,6 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="R187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12233,7 +11749,6 @@
           <t>OpenAI: GPT-4o (2024-05-13)</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12247,7 +11762,6 @@
       <c r="F188" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" s="11" t="n">
         <v>5</v>
       </c>
@@ -12278,7 +11792,6 @@
           <t>2024-05-13</t>
         </is>
       </c>
-      <c r="R188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12291,7 +11804,6 @@
           <t>OpenAI: o1</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12305,7 +11817,6 @@
       <c r="F189" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" s="11" t="n">
         <v>15</v>
       </c>
@@ -12338,7 +11849,6 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12351,7 +11861,6 @@
           <t>OpenAI: GPT-4 Turbo</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12365,7 +11874,6 @@
       <c r="F190" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" s="11" t="n">
         <v>10</v>
       </c>
@@ -12396,7 +11904,6 @@
           <t>2024-04-09</t>
         </is>
       </c>
-      <c r="R190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12409,7 +11916,6 @@
           <t>OpenAI: GPT-5 Pro</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12423,7 +11929,6 @@
       <c r="F191" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" s="11" t="n">
         <v>15</v>
       </c>
@@ -12454,7 +11959,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="R191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12467,7 +11971,6 @@
           <t>OpenAI: o3 Pro</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12481,7 +11984,6 @@
       <c r="F192" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" s="11" t="n">
         <v>20</v>
       </c>
@@ -12512,7 +12014,6 @@
           <t>2025-06-11</t>
         </is>
       </c>
-      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12525,7 +12026,6 @@
           <t>OpenAI: GPT-5.2 Pro</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12539,7 +12039,6 @@
       <c r="F193" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" s="11" t="n">
         <v>21</v>
       </c>
@@ -12570,7 +12069,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="R193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12583,7 +12081,6 @@
           <t>OpenAI: GPT-5.5 Pro</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12597,7 +12094,6 @@
       <c r="F194" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" s="11" t="n">
         <v>30</v>
       </c>
@@ -12628,7 +12124,6 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12641,7 +12136,6 @@
           <t>OpenAI: GPT-5.4 Pro</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12655,7 +12149,6 @@
       <c r="F195" s="10" t="n">
         <v>1050000</v>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" s="11" t="n">
         <v>30</v>
       </c>
@@ -12686,7 +12179,6 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="R195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12699,7 +12191,6 @@
           <t>NVIDIA: Nemotron 3.5 Content Safety (free)</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>no</t>
@@ -12748,7 +12239,6 @@
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="R196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12761,7 +12251,6 @@
           <t>Google: Lyria 3 Pro Preview</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>no</t>
@@ -12810,7 +12299,6 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12823,7 +12311,6 @@
           <t>Google: Lyria 3 Clip Preview</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>no</t>
@@ -12872,7 +12359,6 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="R198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12885,7 +12371,6 @@
           <t>OpenAI: GPT-5 Nano (batch)</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>yes</t>
@@ -12936,7 +12421,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="R199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12949,7 +12433,6 @@
           <t>OpenAI: GPT-6 Luna Pro (batch)</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13002,7 +12485,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13015,7 +12497,6 @@
           <t>OpenAI: GPT-6 Luna (batch)</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13068,7 +12549,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13081,7 +12561,6 @@
           <t>Mistral: Ministral 3 8B 2512 (batch)</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13132,7 +12611,6 @@
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13145,7 +12623,6 @@
           <t>Google: Gemini 2.5 Flash Lite (batch)</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13198,7 +12675,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13211,7 +12687,6 @@
           <t>Mistral: Mistral Small 4 (batch)</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13262,7 +12737,6 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="R204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13275,7 +12749,6 @@
           <t>DeepSeek: DeepSeek V4.1 Flash (batch)</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13326,7 +12799,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="R205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13339,7 +12811,6 @@
           <t>OpenAI: GPT-4.1 Nano (batch)</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13390,7 +12861,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13403,7 +12873,6 @@
           <t>Z.ai: GLM 5.3 Flash (batch)</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13454,7 +12923,6 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="R207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13467,7 +12935,6 @@
           <t>OpenAI: GPT-5.6 Luna Pro (batch)</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13518,7 +12985,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13531,7 +12997,6 @@
           <t>OpenAI: GPT-5.6 Luna (batch)</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13582,7 +13047,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13595,7 +13059,6 @@
           <t>OpenAI: GPT-5.4 Nano (batch)</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13646,7 +13109,6 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="R210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13659,7 +13121,6 @@
           <t>Google: Gemini 3.1 Flash Lite (batch)</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13712,7 +13173,6 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="R211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13725,7 +13185,6 @@
           <t>OpenAI: GPT-5 Mini (batch)</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13776,7 +13235,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="R212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13789,7 +13247,6 @@
           <t>Google: Gemini 3.5 Flash Lite (batch)</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13842,7 +13299,6 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13855,7 +13311,6 @@
           <t>OpenAI: GPT-4o-mini (batch)</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13906,7 +13361,6 @@
           <t>2024-07-18</t>
         </is>
       </c>
-      <c r="R214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13919,7 +13373,6 @@
           <t>Mistral: Mistral Medium 3.1 (batch)</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13970,7 +13423,6 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="R215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13983,7 +13435,6 @@
           <t>Google: Gemini 2.5 Flash (batch)</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14053,7 +13504,6 @@
           <t>Google: Gemma 3 4B</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>no</t>
@@ -14067,7 +13517,6 @@
       <c r="F217" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" s="11" t="n">
         <v>0.05</v>
       </c>
@@ -14098,7 +13547,6 @@
           <t>2025-03-13</t>
         </is>
       </c>
-      <c r="R217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14111,7 +13559,6 @@
           <t>Mistral: Mistral Large 3 2512 (batch)</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14162,7 +13609,6 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="R218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14175,7 +13621,6 @@
           <t>Google: Nano Banana (Gemini 2.5 Flash Image)</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>no</t>
@@ -14189,7 +13634,6 @@
       <c r="F219" s="10" t="n">
         <v>32768</v>
       </c>
-      <c r="G219" t="inlineStr"/>
       <c r="H219" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -14226,7 +13670,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14239,7 +13682,6 @@
           <t>OpenAI: GPT-4.1 Mini (batch)</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14290,7 +13732,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="R220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14303,7 +13744,6 @@
           <t>Google: Gemini 3.8 Flash (batch)</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14358,7 +13798,6 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="R221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14371,7 +13810,6 @@
           <t>Google: Gemini 3.7 Flash (batch)</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14426,7 +13864,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="R222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -14439,7 +13876,6 @@
           <t>Google: Gemini 3.6 Flash (batch)</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14494,7 +13930,6 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="R223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -14507,7 +13942,6 @@
           <t>OpenAI: GPT-5.4 Mini (batch)</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14558,7 +13992,6 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="R224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14571,7 +14004,6 @@
           <t xml:space="preserve">ByteDance: UI-TARS 7B </t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>no</t>
@@ -14585,7 +14017,6 @@
       <c r="F225" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G225" t="inlineStr"/>
       <c r="H225" s="11" t="n">
         <v>0.09999999999999999</v>
       </c>
@@ -14618,7 +14049,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="R225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14631,7 +14061,6 @@
           <t>Anthropic: Claude Haiku 4.5 (batch)</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14684,7 +14113,6 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="R226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14697,7 +14125,6 @@
           <t>OpenAI: GPT-5.1 (batch)</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14748,7 +14175,6 @@
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="R227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14761,7 +14187,6 @@
           <t>OpenAI: GPT-5 (batch)</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14812,7 +14237,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="R228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14825,7 +14249,6 @@
           <t>Perceptron: Perceptron Mk1</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>no</t>
@@ -14839,7 +14262,6 @@
       <c r="F229" s="10" t="n">
         <v>32768</v>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" s="11" t="n">
         <v>0.15</v>
       </c>
@@ -14870,7 +14292,6 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="R229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14883,7 +14304,6 @@
           <t>Google: Gemini 3.5 Flash (batch)</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14936,7 +14356,6 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="R230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14949,7 +14368,6 @@
           <t>Meta: Llama Guard 4 12B</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>no</t>
@@ -14963,7 +14381,6 @@
       <c r="F231" s="10" t="n">
         <v>163840</v>
       </c>
-      <c r="G231" t="inlineStr"/>
       <c r="H231" s="11" t="n">
         <v>0.18</v>
       </c>
@@ -14994,7 +14411,6 @@
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="R231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15007,7 +14423,6 @@
           <t>OpenAI: o4 Mini (batch)</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15058,7 +14473,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="R232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15071,7 +14485,6 @@
           <t>NVIDIA: Nemotron 3.5 Content Safety</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>no</t>
@@ -15085,7 +14498,6 @@
       <c r="F233" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G233" t="inlineStr"/>
       <c r="H233" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -15116,7 +14528,6 @@
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="R233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15129,7 +14540,6 @@
           <t>MiniMax: MiniMax-01</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>no</t>
@@ -15143,7 +14553,6 @@
       <c r="F234" s="10" t="n">
         <v>1000192</v>
       </c>
-      <c r="G234" t="inlineStr"/>
       <c r="H234" s="11" t="n">
         <v>0.2</v>
       </c>
@@ -15174,7 +14583,6 @@
           <t>2025-01-15</t>
         </is>
       </c>
-      <c r="R234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15187,7 +14595,6 @@
           <t>Google: Gemini 2.5 Pro (batch)</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15257,7 +14664,6 @@
           <t>OpenAI: GPT-5.2 (batch)</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15308,7 +14714,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="R236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15321,7 +14726,6 @@
           <t>OpenAI: GPT-5.6 Terra Pro (batch)</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15372,7 +14776,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15385,7 +14788,6 @@
           <t>OpenAI: GPT-5.6 Terra (batch)</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15436,7 +14838,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -15449,7 +14850,6 @@
           <t>OpenAI: GPT-6 Sol Pro (batch)</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15502,7 +14902,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15515,7 +14914,6 @@
           <t>OpenAI: GPT-6 Sol (batch)</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15568,7 +14966,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15581,7 +14978,6 @@
           <t>OpenAI: GPT-5.6 Sol Pro (batch)</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15634,7 +15030,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -15647,7 +15042,6 @@
           <t>OpenAI: GPT-5.6 Sol (batch)</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15700,7 +15094,6 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="R242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -15713,7 +15106,6 @@
           <t>Anthropic: Claude Sonnet 5 (batch)</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15766,7 +15158,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="R243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -15779,7 +15170,6 @@
           <t>Google: Nano Banana 2 Lite (Gemini 3.1 Flash Lite Image)</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>no</t>
@@ -15793,7 +15183,6 @@
       <c r="F244" s="10" t="n">
         <v>65536</v>
       </c>
-      <c r="G244" t="inlineStr"/>
       <c r="H244" s="11" t="n">
         <v>0.25</v>
       </c>
@@ -15824,7 +15213,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="R244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -15837,7 +15225,6 @@
           <t>Google: Gemini 3 Flash Preview (batch)</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15888,7 +15275,6 @@
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="R245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -15901,7 +15287,6 @@
           <t>SpaceXAI: Grok 4.3 (batch)</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>yes</t>
@@ -15952,7 +15337,6 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="R246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -15965,7 +15349,6 @@
           <t>OpenAI: GPT-5.4 (batch)</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16016,7 +15399,6 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="R247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16029,7 +15411,6 @@
           <t>SpaceXAI: Grok 4.20 Multi-Agent</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>no</t>
@@ -16043,7 +15424,6 @@
       <c r="F248" s="10" t="n">
         <v>2000000</v>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" s="11" t="n">
         <v>1.25</v>
       </c>
@@ -16076,7 +15456,6 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="R248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -16089,7 +15468,6 @@
           <t>Anthropic: Claude Sonnet 4.6 (batch)</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16142,7 +15520,6 @@
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="R249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16155,7 +15532,6 @@
           <t>Anthropic: Claude Sonnet 4.5 (batch)</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16208,7 +15584,6 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="R250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16221,7 +15596,6 @@
           <t>OpenAI: o3 (batch)</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16272,7 +15646,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="R251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16285,7 +15658,6 @@
           <t>OpenAI: GPT-4.1 (batch)</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16336,7 +15708,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="R252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16349,7 +15720,6 @@
           <t>Anthropic: Claude Opus 5.5 (batch)</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16402,7 +15772,6 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="R253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16415,7 +15784,6 @@
           <t>Google: Nano Banana Pro (Gemini 3 Pro Image Preview)</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>no</t>
@@ -16429,7 +15797,6 @@
       <c r="F254" s="10" t="n">
         <v>65536</v>
       </c>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" s="11" t="n">
         <v>2</v>
       </c>
@@ -16466,7 +15833,6 @@
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="R254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -16479,7 +15845,6 @@
           <t xml:space="preserve">Baidu: ERNIE 4.5 VL 424B A47B </t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>no</t>
@@ -16493,7 +15858,6 @@
       <c r="F255" s="10" t="n">
         <v>123000</v>
       </c>
-      <c r="G255" t="inlineStr"/>
       <c r="H255" s="11" t="n">
         <v>0.42</v>
       </c>
@@ -16541,7 +15905,6 @@
           <t>Qwen: Qwen2.5 VL 72B Instruct</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>no</t>
@@ -16555,7 +15918,6 @@
       <c r="F256" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" s="11" t="n">
         <v>0.7999999999999999</v>
       </c>
@@ -16588,7 +15950,6 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="R256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -16601,7 +15962,6 @@
           <t>OpenAI: GPT-5 Image Mini</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>no</t>
@@ -16615,7 +15975,6 @@
       <c r="F257" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G257" t="inlineStr"/>
       <c r="H257" s="11" t="n">
         <v>2.5</v>
       </c>
@@ -16648,7 +16007,6 @@
           <t>2025-10-16</t>
         </is>
       </c>
-      <c r="R257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -16661,7 +16019,6 @@
           <t>MoonshotAI: Kimi K3 (batch)</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16712,7 +16069,6 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="R258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -16725,7 +16081,6 @@
           <t>Google: Nano Banana 2 (Gemini 3.1 Flash Image)</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>no</t>
@@ -16739,7 +16094,6 @@
       <c r="F259" s="10" t="n">
         <v>131072</v>
       </c>
-      <c r="G259" t="inlineStr"/>
       <c r="H259" s="11" t="n">
         <v>0.5</v>
       </c>
@@ -16770,7 +16124,6 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="R259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -16783,7 +16136,6 @@
           <t>Google: Nano Banana 2 (Gemini 3.1 Flash Image Preview)</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>no</t>
@@ -16797,7 +16149,6 @@
       <c r="F260" s="10" t="n">
         <v>65536</v>
       </c>
-      <c r="G260" t="inlineStr"/>
       <c r="H260" s="11" t="n">
         <v>0.5</v>
       </c>
@@ -16828,7 +16179,6 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="R260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -16841,7 +16191,6 @@
           <t>OpenAI: GPT-5.5 (batch)</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16892,7 +16241,6 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="R261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -16905,7 +16253,6 @@
           <t>Anthropic: Claude Opus 5 (batch)</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16958,7 +16305,6 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="R262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -16971,7 +16317,6 @@
           <t>Anthropic: Claude Opus 4.8 (batch)</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17024,7 +16369,6 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="R263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17037,7 +16381,6 @@
           <t>Anthropic: Claude Opus 4.7 (batch)</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17090,7 +16433,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="R264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17103,7 +16445,6 @@
           <t>Anthropic: Claude Opus 4.6 (batch)</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17156,7 +16497,6 @@
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="R265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -17169,7 +16509,6 @@
           <t>Anthropic: Claude Opus 4.5 (batch)</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17222,7 +16561,6 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="R266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -17235,7 +16573,6 @@
           <t>OpenAI: GPT-4o (batch)</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17286,7 +16623,6 @@
           <t>2024-05-13</t>
         </is>
       </c>
-      <c r="R267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17299,7 +16635,6 @@
           <t>Mistral: Mistral Medium 3.5 (batch)</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17348,7 +16683,6 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="R268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -17361,7 +16695,6 @@
           <t>Anthropic: Claude Fable 5.1 (batch)</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17414,7 +16747,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="R269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17427,7 +16759,6 @@
           <t>Perplexity: Sonar</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>no</t>
@@ -17441,7 +16772,6 @@
       <c r="F270" s="10" t="n">
         <v>127072</v>
       </c>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" s="11" t="n">
         <v>1</v>
       </c>
@@ -17472,7 +16802,6 @@
           <t>2025-01-27</t>
         </is>
       </c>
-      <c r="R270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -17485,7 +16814,6 @@
           <t>Google: Gemini 3.1 Pro Preview (batch)</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17536,7 +16864,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="R271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -17549,7 +16876,6 @@
           <t>OpenAI: GPT-6 Astra (batch)</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17602,7 +16928,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="R272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -17615,7 +16940,6 @@
           <t>OpenAI: GPT-6 Astra Pro (batch)</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17668,7 +16992,6 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="R273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -17681,7 +17004,6 @@
           <t>Anthropic: Claude Fable 5 (batch)</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17734,7 +17056,6 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="R274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -17747,7 +17068,6 @@
           <t>Anthropic: Claude Opus 4.1 (batch)</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>yes</t>
@@ -17800,7 +17120,6 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="R275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -17813,7 +17132,6 @@
           <t>Perplexity: Sonar Reasoning Pro</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>no</t>
@@ -17827,7 +17145,6 @@
       <c r="F276" s="10" t="n">
         <v>128000</v>
       </c>
-      <c r="G276" t="inlineStr"/>
       <c r="H276" s="11" t="n">
         <v>2</v>
       </c>
@@ -17858,7 +17175,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="R276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -17871,7 +17187,6 @@
           <t>OpenAI: GPT-5 Image</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>no</t>
@@ -17885,7 +17200,6 @@
       <c r="F277" s="10" t="n">
         <v>400000</v>
       </c>
-      <c r="G277" t="inlineStr"/>
       <c r="H277" s="11" t="n">
         <v>10</v>
       </c>
@@ -17918,7 +17232,6 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="R277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -17931,7 +17244,6 @@
           <t>OpenAI: GPT-5.4 Image 2</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>no</t>
@@ -17945,7 +17257,6 @@
       <c r="F278" s="10" t="n">
         <v>272000</v>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" s="11" t="n">
         <v>8</v>
       </c>
@@ -17978,7 +17289,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="R278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -17991,7 +17301,6 @@
           <t>Perplexity: Sonar Pro Search</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>no</t>
@@ -18005,7 +17314,6 @@
       <c r="F279" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" s="11" t="n">
         <v>3</v>
       </c>
@@ -18036,7 +17344,6 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="R279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18049,7 +17356,6 @@
           <t>Perplexity: Sonar Pro</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>no</t>
@@ -18063,7 +17369,6 @@
       <c r="F280" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" s="11" t="n">
         <v>3</v>
       </c>
@@ -18094,7 +17399,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="R280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18107,7 +17411,6 @@
           <t>OpenAI: GPT-4 Turbo (batch)</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18156,7 +17459,6 @@
           <t>2024-04-09</t>
         </is>
       </c>
-      <c r="R281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18169,7 +17471,6 @@
           <t>OpenAI: GPT-5 Pro (batch)</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18218,7 +17519,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="R282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18231,7 +17531,6 @@
           <t>OpenAI: GPT-5.2 Pro (batch)</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18280,7 +17579,6 @@
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="R283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18293,7 +17591,6 @@
           <t>OpenAI: GPT-5.5 Pro (batch)</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18342,7 +17639,6 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="R284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -18355,7 +17651,6 @@
           <t>OpenAI: GPT-5.4 Pro (batch)</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18404,7 +17699,6 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="R285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18417,7 +17711,6 @@
           <t>OpenAI: o1-pro</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>no</t>
@@ -18431,7 +17724,6 @@
       <c r="F286" s="10" t="n">
         <v>200000</v>
       </c>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" s="11" t="n">
         <v>150</v>
       </c>
@@ -18462,7 +17754,6 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="R286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18475,7 +17766,6 @@
           <t>TypeSafe: Jev Router</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>no</t>
@@ -18520,7 +17810,6 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="R287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -18533,7 +17822,6 @@
           <t>Auto Router (Beta)</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18578,7 +17866,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="R288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18591,7 +17878,6 @@
           <t>Auto Router</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>yes</t>
@@ -18636,7 +17922,6 @@
           <t>2023-11-08</t>
         </is>
       </c>
-      <c r="R289" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R289"/>

--- a/notes/costs/vision_models_2026-09-28.xlsx
+++ b/notes/costs/vision_models_2026-09-28.xlsx
@@ -11250,11 +11250,7 @@
           <t>Mistral: Mistral Medium 3.5</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>cache read 10% per Mistral (not on OpenRouter)</t>
-        </is>
-      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>yes</t>
@@ -11267,6 +11263,11 @@
       </c>
       <c r="F180" s="10" t="n">
         <v>262144</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>cache read 10% per Mistral (not on OpenRouter)</t>
+        </is>
       </c>
       <c r="H180" s="11" t="n">
         <v>1.5</v>
